--- a/diseases/d104/2015-2019.xlsx
+++ b/diseases/d104/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6102,6 +6282,11 @@
       <c r="S38" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">

--- a/diseases/d104/2015-2019.xlsx
+++ b/diseases/d104/2015-2019.xlsx
@@ -765,17 +765,15 @@
       <c r="O2" t="n">
         <v>3</v>
       </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0.0008881255837640211</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -788,22 +786,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,17 +906,15 @@
       <c r="O3" t="n">
         <v>3</v>
       </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0.0008881255837640211</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -941,22 +927,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1071,17 +1047,15 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1094,22 +1068,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1224,17 +1188,15 @@
       <c r="O5" t="n">
         <v>2</v>
       </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.0005920837225093475</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1247,22 +1209,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1377,17 +1329,15 @@
       <c r="O6" t="n">
         <v>4</v>
       </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.001184167445018695</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1400,22 +1350,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1530,17 +1470,15 @@
       <c r="O7" t="n">
         <v>4</v>
       </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.001184167445018695</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1553,22 +1491,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1683,17 +1611,15 @@
       <c r="O8" t="n">
         <v>6</v>
       </c>
+      <c r="P8" t="n">
+        <v>6</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.001776251167528042</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1706,22 +1632,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1836,17 +1752,15 @@
       <c r="O9" t="n">
         <v>15</v>
       </c>
+      <c r="P9" t="n">
+        <v>15</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.004440627918820105</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1859,22 +1773,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1989,17 +1893,15 @@
       <c r="O10" t="n">
         <v>8</v>
       </c>
+      <c r="P10" t="n">
+        <v>8</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.00236833489003739</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2012,22 +1914,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2142,17 +2034,15 @@
       <c r="O11" t="n">
         <v>3</v>
       </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.0008881255837640211</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2165,22 +2055,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2295,17 +2175,15 @@
       <c r="O12" t="n">
         <v>8</v>
       </c>
+      <c r="P12" t="n">
+        <v>8</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.00236833489003739</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2318,22 +2196,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2448,17 +2316,15 @@
       <c r="O13" t="n">
         <v>6</v>
       </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0.001776251167528042</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2471,22 +2337,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2601,17 +2457,15 @@
       <c r="O14" t="n">
         <v>4</v>
       </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.001184167445018695</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2624,22 +2478,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2754,17 +2598,15 @@
       <c r="O15" t="n">
         <v>5</v>
       </c>
+      <c r="P15" t="n">
+        <v>5</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.001480209306273368</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2777,22 +2619,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2907,17 +2739,15 @@
       <c r="O16" t="n">
         <v>3</v>
       </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0.0008881255837640211</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2930,22 +2760,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3060,17 +2880,15 @@
       <c r="O17" t="n">
         <v>5</v>
       </c>
+      <c r="P17" t="n">
+        <v>5</v>
+      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0.001480209306273368</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3083,22 +2901,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3213,17 +3021,15 @@
       <c r="O18" t="n">
         <v>5</v>
       </c>
+      <c r="P18" t="n">
+        <v>5</v>
+      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.001480209306273368</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3236,22 +3042,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3366,17 +3162,15 @@
       <c r="O19" t="n">
         <v>3</v>
       </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.0008881255837640211</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3389,22 +3183,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3519,17 +3303,15 @@
       <c r="O20" t="n">
         <v>3</v>
       </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.0008881255837640211</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3542,22 +3324,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3672,17 +3444,15 @@
       <c r="O21" t="n">
         <v>2</v>
       </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.0005920837225093475</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3695,22 +3465,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3825,17 +3585,15 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3848,22 +3606,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3978,17 +3726,15 @@
       <c r="O23" t="n">
         <v>2</v>
       </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0.0005920837225093475</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4001,22 +3747,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4131,17 +3867,15 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4154,22 +3888,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4284,17 +4008,15 @@
       <c r="O25" t="n">
         <v>2</v>
       </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0.0005920837225093475</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4307,22 +4029,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4437,17 +4149,15 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4460,22 +4170,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4590,17 +4290,15 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4613,22 +4311,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4743,17 +4431,15 @@
       <c r="O28" t="n">
         <v>4</v>
       </c>
+      <c r="P28" t="n">
+        <v>4</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0.001184167445018695</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4766,22 +4452,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4896,17 +4572,15 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4919,22 +4593,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5049,17 +4713,15 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5072,22 +4734,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5202,17 +4854,15 @@
       <c r="O31" t="n">
         <v>2</v>
       </c>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0.0005920837225093475</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5225,22 +4875,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5355,17 +4995,15 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5378,22 +5016,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5508,17 +5136,15 @@
       <c r="O33" t="n">
         <v>2</v>
       </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0.0005920837225093475</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5531,22 +5157,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5661,17 +5277,15 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5684,22 +5298,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5814,17 +5418,15 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5837,22 +5439,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5967,17 +5559,15 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5990,22 +5580,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6120,17 +5700,15 @@
       <c r="O37" t="n">
         <v>3</v>
       </c>
+      <c r="P37" t="n">
+        <v>3</v>
+      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0.0008881255837640211</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6143,22 +5721,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6273,17 +5841,15 @@
       <c r="O38" t="n">
         <v>9</v>
       </c>
+      <c r="P38" t="n">
+        <v>9</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0.002664376751292063</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6296,22 +5862,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
